--- a/output/graficos_otras_relaciones/plot_comunal_d_otrasrel_a_2023_metropolitana.xlsx
+++ b/output/graficos_otras_relaciones/plot_comunal_d_otrasrel_a_2023_metropolitana.xlsx
@@ -398,22 +398,22 @@
         </is>
       </c>
       <c r="B2">
+        <v>17.57577717921876</v>
+      </c>
+      <c r="C2">
         <v>19.59973652948165</v>
-      </c>
-      <c r="C2">
-        <v>17.57577717921876</v>
       </c>
       <c r="D2">
         <v>5.10210940078615</v>
       </c>
       <c r="E2">
-        <v>14.28807226565431</v>
+        <v>12.81261990863899</v>
       </c>
       <c r="F2">
         <v>72.8993078257067</v>
       </c>
       <c r="G2">
-        <v>12.81261990863899</v>
+        <v>14.28807226565431</v>
       </c>
     </row>
     <row r="3">
@@ -423,22 +423,22 @@
         </is>
       </c>
       <c r="B3">
+        <v>27.55531749843005</v>
+      </c>
+      <c r="C3">
         <v>30.93531823722803</v>
-      </c>
-      <c r="C3">
-        <v>27.55531749843005</v>
       </c>
       <c r="D3">
         <v>3.232551197086393</v>
       </c>
       <c r="E3">
-        <v>19.51870411373966</v>
+        <v>17.3860855378161</v>
       </c>
       <c r="F3">
         <v>63.09521034844423</v>
       </c>
       <c r="G3">
-        <v>17.3860855378161</v>
+        <v>19.51870411373966</v>
       </c>
     </row>
     <row r="4">
@@ -448,22 +448,22 @@
         </is>
       </c>
       <c r="B4">
+        <v>27.584875667083</v>
+      </c>
+      <c r="C4">
         <v>31.99727489496991</v>
-      </c>
-      <c r="C4">
-        <v>27.584875667083</v>
       </c>
       <c r="D4">
         <v>3.125266146202981</v>
       </c>
       <c r="E4">
-        <v>20.05066029143898</v>
+        <v>17.28568989071039</v>
       </c>
       <c r="F4">
         <v>62.66364981785064</v>
       </c>
       <c r="G4">
-        <v>17.28568989071039</v>
+        <v>20.05066029143898</v>
       </c>
     </row>
     <row r="5">
@@ -473,22 +473,22 @@
         </is>
       </c>
       <c r="B5">
+        <v>26.30363744180472</v>
+      </c>
+      <c r="C5">
         <v>36.56240931629215</v>
-      </c>
-      <c r="C5">
-        <v>26.30363744180472</v>
       </c>
       <c r="D5">
         <v>2.735049518616929</v>
       </c>
       <c r="E5">
-        <v>22.44937483538106</v>
+        <v>16.15047332785895</v>
       </c>
       <c r="F5">
         <v>61.40015183675999</v>
       </c>
       <c r="G5">
-        <v>16.15047332785895</v>
+        <v>22.44937483538106</v>
       </c>
     </row>
     <row r="6">
@@ -498,22 +498,22 @@
         </is>
       </c>
       <c r="B6">
+        <v>28.54175742900275</v>
+      </c>
+      <c r="C6">
         <v>35.92972715575323</v>
-      </c>
-      <c r="C6">
-        <v>28.54175742900275</v>
       </c>
       <c r="D6">
         <v>2.783210670276062</v>
       </c>
       <c r="E6">
-        <v>21.84556626728678</v>
+        <v>17.35362059937783</v>
       </c>
       <c r="F6">
         <v>60.80081313333538</v>
       </c>
       <c r="G6">
-        <v>17.35362059937783</v>
+        <v>21.84556626728678</v>
       </c>
     </row>
     <row r="7">
@@ -523,22 +523,22 @@
         </is>
       </c>
       <c r="B7">
+        <v>25.08145580589255</v>
+      </c>
+      <c r="C7">
         <v>25.96707105719237</v>
-      </c>
-      <c r="C7">
-        <v>25.08145580589255</v>
       </c>
       <c r="D7">
         <v>3.851031168657812</v>
       </c>
       <c r="E7">
-        <v>17.19121106075383</v>
+        <v>16.60489931730825</v>
       </c>
       <c r="F7">
         <v>66.20388962193792</v>
       </c>
       <c r="G7">
-        <v>16.60489931730825</v>
+        <v>17.19121106075383</v>
       </c>
     </row>
     <row r="8">
@@ -548,22 +548,22 @@
         </is>
       </c>
       <c r="B8">
+        <v>28.58309817317689</v>
+      </c>
+      <c r="C8">
         <v>25.2562008020199</v>
-      </c>
-      <c r="C8">
-        <v>28.58309817317689</v>
       </c>
       <c r="D8">
         <v>3.959423698912085</v>
       </c>
       <c r="E8">
-        <v>16.41726201969492</v>
+        <v>18.57984166827573</v>
       </c>
       <c r="F8">
         <v>65.00289631202935</v>
       </c>
       <c r="G8">
-        <v>18.57984166827573</v>
+        <v>16.41726201969492</v>
       </c>
     </row>
     <row r="9">
@@ -573,22 +573,22 @@
         </is>
       </c>
       <c r="B9">
+        <v>24.70674666340149</v>
+      </c>
+      <c r="C9">
         <v>25.05816089139219</v>
-      </c>
-      <c r="C9">
-        <v>24.70674666340149</v>
       </c>
       <c r="D9">
         <v>3.990715856340093</v>
       </c>
       <c r="E9">
-        <v>16.73166384603435</v>
+        <v>16.49701994064408</v>
       </c>
       <c r="F9">
         <v>66.77131621332155</v>
       </c>
       <c r="G9">
-        <v>16.49701994064408</v>
+        <v>16.73166384603435</v>
       </c>
     </row>
     <row r="10">
@@ -598,22 +598,22 @@
         </is>
       </c>
       <c r="B10">
+        <v>24.76178709866724</v>
+      </c>
+      <c r="C10">
         <v>33.34362886661622</v>
-      </c>
-      <c r="C10">
-        <v>24.76178709866724</v>
       </c>
       <c r="D10">
         <v>2.999073688110787</v>
       </c>
       <c r="E10">
-        <v>21.08949188302174</v>
+        <v>15.66156791498173</v>
       </c>
       <c r="F10">
         <v>63.24894020199652</v>
       </c>
       <c r="G10">
-        <v>15.66156791498173</v>
+        <v>21.08949188302174</v>
       </c>
     </row>
     <row r="11">
@@ -623,22 +623,22 @@
         </is>
       </c>
       <c r="B11">
+        <v>24.55055726225531</v>
+      </c>
+      <c r="C11">
         <v>35.95159487905094</v>
-      </c>
-      <c r="C11">
-        <v>24.55055726225531</v>
       </c>
       <c r="D11">
         <v>2.78151776955715</v>
       </c>
       <c r="E11">
-        <v>22.39944723445149</v>
+        <v>15.29609225466396</v>
       </c>
       <c r="F11">
-        <v>62.30446051088456</v>
+        <v>62.30446051088455</v>
       </c>
       <c r="G11">
-        <v>15.29609225466396</v>
+        <v>22.39944723445148</v>
       </c>
     </row>
     <row r="12">
@@ -648,22 +648,22 @@
         </is>
       </c>
       <c r="B12">
+        <v>27.06691464736342</v>
+      </c>
+      <c r="C12">
         <v>37.74034280209267</v>
-      </c>
-      <c r="C12">
-        <v>27.06691464736342</v>
       </c>
       <c r="D12">
         <v>2.649684464298376</v>
       </c>
       <c r="E12">
+        <v>16.4233754424707</v>
+      </c>
+      <c r="F12">
+        <v>60.67693956418668</v>
+      </c>
+      <c r="G12">
         <v>22.89968499334264</v>
-      </c>
-      <c r="F12">
-        <v>60.67693956418666</v>
-      </c>
-      <c r="G12">
-        <v>16.42337544247069</v>
       </c>
     </row>
     <row r="13">
@@ -673,22 +673,22 @@
         </is>
       </c>
       <c r="B13">
+        <v>32.06073060978634</v>
+      </c>
+      <c r="C13">
         <v>28.95599333876626</v>
-      </c>
-      <c r="C13">
-        <v>32.06073060978634</v>
       </c>
       <c r="D13">
         <v>3.45351647343143</v>
       </c>
       <c r="E13">
-        <v>17.98322101499106</v>
+        <v>19.91142896437904</v>
       </c>
       <c r="F13">
         <v>62.1053500206299</v>
       </c>
       <c r="G13">
-        <v>19.91142896437904</v>
+        <v>17.98322101499106</v>
       </c>
     </row>
     <row r="14">
@@ -698,22 +698,22 @@
         </is>
       </c>
       <c r="B14">
+        <v>24.75319473245777</v>
+      </c>
+      <c r="C14">
         <v>40.50619450204711</v>
-      </c>
-      <c r="C14">
-        <v>24.75319473245777</v>
       </c>
       <c r="D14">
         <v>2.468758204253085</v>
       </c>
       <c r="E14">
+        <v>14.97838933516372</v>
+      </c>
+      <c r="F14">
+        <v>60.51093403116655</v>
+      </c>
+      <c r="G14">
         <v>24.51067663366974</v>
-      </c>
-      <c r="F14">
-        <v>60.51093403116656</v>
-      </c>
-      <c r="G14">
-        <v>14.97838933516372</v>
       </c>
     </row>
     <row r="15">
@@ -723,22 +723,22 @@
         </is>
       </c>
       <c r="B15">
+        <v>20.6620319907376</v>
+      </c>
+      <c r="C15">
         <v>39.15553631684077</v>
-      </c>
-      <c r="C15">
-        <v>20.6620319907376</v>
       </c>
       <c r="D15">
         <v>2.553917259383574</v>
       </c>
       <c r="E15">
-        <v>24.50014521650312</v>
+        <v>12.92851105766564</v>
       </c>
       <c r="F15">
         <v>62.57134372583124</v>
       </c>
       <c r="G15">
-        <v>12.92851105766564</v>
+        <v>24.50014521650312</v>
       </c>
     </row>
     <row r="16">
@@ -748,22 +748,22 @@
         </is>
       </c>
       <c r="B16">
+        <v>27.09688716477418</v>
+      </c>
+      <c r="C16">
         <v>25.48591748494767</v>
-      </c>
-      <c r="C16">
-        <v>27.09688716477418</v>
       </c>
       <c r="D16">
         <v>3.923735531948628</v>
       </c>
       <c r="E16">
-        <v>16.70300761835821</v>
+        <v>17.75880789908103</v>
       </c>
       <c r="F16">
         <v>65.53818448256075</v>
       </c>
       <c r="G16">
-        <v>17.75880789908103</v>
+        <v>16.70300761835821</v>
       </c>
     </row>
     <row r="17">
@@ -773,22 +773,22 @@
         </is>
       </c>
       <c r="B17">
+        <v>27.08032178995663</v>
+      </c>
+      <c r="C17">
         <v>34.63327257871913</v>
-      </c>
-      <c r="C17">
-        <v>27.08032178995663</v>
       </c>
       <c r="D17">
         <v>2.887396787950277</v>
       </c>
       <c r="E17">
-        <v>21.416426190962</v>
+        <v>16.74585361588014</v>
       </c>
       <c r="F17">
         <v>61.83772019315786</v>
       </c>
       <c r="G17">
-        <v>16.74585361588014</v>
+        <v>21.416426190962</v>
       </c>
     </row>
     <row r="18">
@@ -798,22 +798,22 @@
         </is>
       </c>
       <c r="B18">
+        <v>25.75039758935297</v>
+      </c>
+      <c r="C18">
         <v>35.84498200385034</v>
-      </c>
-      <c r="C18">
-        <v>25.75039758935297</v>
       </c>
       <c r="D18">
         <v>2.789790771529983</v>
       </c>
       <c r="E18">
-        <v>22.18193496255012</v>
+        <v>15.93510758424929</v>
       </c>
       <c r="F18">
         <v>61.88295745320059</v>
       </c>
       <c r="G18">
-        <v>15.93510758424929</v>
+        <v>22.18193496255012</v>
       </c>
     </row>
     <row r="19">
@@ -823,22 +823,22 @@
         </is>
       </c>
       <c r="B19">
+        <v>22.50593237097093</v>
+      </c>
+      <c r="C19">
         <v>35.78702788214356</v>
-      </c>
-      <c r="C19">
-        <v>22.50593237097093</v>
       </c>
       <c r="D19">
         <v>2.794308606161072</v>
       </c>
       <c r="E19">
-        <v>22.60809819016537</v>
+        <v>14.21789846812099</v>
       </c>
       <c r="F19">
         <v>63.17400334171365</v>
       </c>
       <c r="G19">
-        <v>14.21789846812099</v>
+        <v>22.60809819016537</v>
       </c>
     </row>
     <row r="20">
@@ -848,22 +848,22 @@
         </is>
       </c>
       <c r="B20">
+        <v>25.20578916362826</v>
+      </c>
+      <c r="C20">
         <v>33.74369098985782</v>
-      </c>
-      <c r="C20">
-        <v>25.20578916362826</v>
       </c>
       <c r="D20">
         <v>2.96351694395425</v>
       </c>
       <c r="E20">
-        <v>21.22919241841745</v>
+        <v>15.85773614313733</v>
       </c>
       <c r="F20">
         <v>62.91307143844522</v>
       </c>
       <c r="G20">
-        <v>15.85773614313733</v>
+        <v>21.22919241841745</v>
       </c>
     </row>
     <row r="21">
@@ -873,22 +873,22 @@
         </is>
       </c>
       <c r="B21">
+        <v>19.36217046993852</v>
+      </c>
+      <c r="C21">
         <v>32.7849848911118</v>
-      </c>
-      <c r="C21">
-        <v>19.36217046993852</v>
       </c>
       <c r="D21">
         <v>3.050176790751261</v>
       </c>
       <c r="E21">
-        <v>21.5482075976458</v>
+        <v>12.72594970572499</v>
       </c>
       <c r="F21">
         <v>65.72584269662921</v>
       </c>
       <c r="G21">
-        <v>12.72594970572499</v>
+        <v>21.5482075976458</v>
       </c>
     </row>
     <row r="22">
@@ -898,22 +898,22 @@
         </is>
       </c>
       <c r="B22">
+        <v>27.05221168908771</v>
+      </c>
+      <c r="C22">
         <v>42.93373815022367</v>
-      </c>
-      <c r="C22">
-        <v>27.05221168908771</v>
       </c>
       <c r="D22">
         <v>2.329170584916306</v>
       </c>
       <c r="E22">
-        <v>25.25722754781155</v>
+        <v>15.91438099128799</v>
       </c>
       <c r="F22">
         <v>58.82839146090047</v>
       </c>
       <c r="G22">
-        <v>15.91438099128799</v>
+        <v>25.25722754781155</v>
       </c>
     </row>
     <row r="23">
@@ -923,22 +923,22 @@
         </is>
       </c>
       <c r="B23">
+        <v>25.59936888284567</v>
+      </c>
+      <c r="C23">
         <v>29.65352694434111</v>
-      </c>
-      <c r="C23">
-        <v>25.59936888284567</v>
       </c>
       <c r="D23">
         <v>3.372280140156595</v>
       </c>
       <c r="E23">
-        <v>19.10014417853351</v>
+        <v>16.48881893407033</v>
       </c>
       <c r="F23">
         <v>64.41103688739615</v>
       </c>
       <c r="G23">
-        <v>16.48881893407033</v>
+        <v>19.10014417853351</v>
       </c>
     </row>
     <row r="24">
@@ -948,22 +948,22 @@
         </is>
       </c>
       <c r="B24">
+        <v>14.95287804967229</v>
+      </c>
+      <c r="C24">
         <v>32.35646315712496</v>
-      </c>
-      <c r="C24">
-        <v>14.95287804967229</v>
       </c>
       <c r="D24">
         <v>3.090572647399497</v>
       </c>
       <c r="E24">
-        <v>21.9649771644162</v>
+        <v>10.15066521048451</v>
       </c>
       <c r="F24">
         <v>67.88435762509928</v>
       </c>
       <c r="G24">
-        <v>10.15066521048451</v>
+        <v>21.9649771644162</v>
       </c>
     </row>
     <row r="25">
@@ -973,22 +973,22 @@
         </is>
       </c>
       <c r="B25">
+        <v>28.2897550782866</v>
+      </c>
+      <c r="C25">
         <v>29.14098599746173</v>
-      </c>
-      <c r="C25">
-        <v>28.2897550782866</v>
       </c>
       <c r="D25">
         <v>3.431592877767084</v>
       </c>
       <c r="E25">
-        <v>18.51035305959746</v>
+        <v>17.96965121613376</v>
       </c>
       <c r="F25">
         <v>63.51999572426878</v>
       </c>
       <c r="G25">
-        <v>17.96965121613376</v>
+        <v>18.51035305959746</v>
       </c>
     </row>
     <row r="26">
@@ -998,22 +998,22 @@
         </is>
       </c>
       <c r="B26">
+        <v>28.08205271817132</v>
+      </c>
+      <c r="C26">
         <v>20.56498757307383</v>
-      </c>
-      <c r="C26">
-        <v>28.08205271817132</v>
       </c>
       <c r="D26">
         <v>4.862633621570096</v>
       </c>
       <c r="E26">
+        <v>18.89176714393368</v>
+      </c>
+      <c r="F26">
+        <v>67.27345516201959</v>
+      </c>
+      <c r="G26">
         <v>13.83477769404672</v>
-      </c>
-      <c r="F26">
-        <v>67.2734551620196</v>
-      </c>
-      <c r="G26">
-        <v>18.89176714393369</v>
       </c>
     </row>
     <row r="27">
@@ -1023,22 +1023,22 @@
         </is>
       </c>
       <c r="B27">
+        <v>24.83400514730942</v>
+      </c>
+      <c r="C27">
         <v>30.67702396201803</v>
-      </c>
-      <c r="C27">
-        <v>24.83400514730942</v>
       </c>
       <c r="D27">
         <v>3.259768617836347</v>
       </c>
       <c r="E27">
+        <v>15.9692886668833</v>
+      </c>
+      <c r="F27">
+        <v>64.30412078984955</v>
+      </c>
+      <c r="G27">
         <v>19.72659054326716</v>
-      </c>
-      <c r="F27">
-        <v>64.30412078984953</v>
-      </c>
-      <c r="G27">
-        <v>15.9692886668833</v>
       </c>
     </row>
     <row r="28">
@@ -1048,22 +1048,22 @@
         </is>
       </c>
       <c r="B28">
+        <v>25.72203087720602</v>
+      </c>
+      <c r="C28">
         <v>31.6598122858973</v>
-      </c>
-      <c r="C28">
-        <v>25.72203087720602</v>
       </c>
       <c r="D28">
         <v>3.158578424185555</v>
       </c>
       <c r="E28">
-        <v>20.11655960407486</v>
+        <v>16.34370926165154</v>
       </c>
       <c r="F28">
         <v>63.53973113427359</v>
       </c>
       <c r="G28">
-        <v>16.34370926165154</v>
+        <v>20.11655960407486</v>
       </c>
     </row>
     <row r="29">
@@ -1073,22 +1073,22 @@
         </is>
       </c>
       <c r="B29">
+        <v>30.15543375867089</v>
+      </c>
+      <c r="C29">
         <v>29.28299220690246</v>
-      </c>
-      <c r="C29">
-        <v>30.15543375867089</v>
       </c>
       <c r="D29">
         <v>3.414951562785597</v>
       </c>
       <c r="E29">
-        <v>18.36633297748773</v>
+        <v>18.9135295183999</v>
       </c>
       <c r="F29">
         <v>62.72013750411237</v>
       </c>
       <c r="G29">
-        <v>18.9135295183999</v>
+        <v>18.36633297748773</v>
       </c>
     </row>
     <row r="30">
@@ -1098,22 +1098,22 @@
         </is>
       </c>
       <c r="B30">
+        <v>25.17171780388966</v>
+      </c>
+      <c r="C30">
         <v>37.43213430757436</v>
-      </c>
-      <c r="C30">
-        <v>25.17171780388966</v>
       </c>
       <c r="D30">
         <v>2.671501421167029</v>
       </c>
       <c r="E30">
-        <v>23.02044743805629</v>
+        <v>15.48039451527544</v>
       </c>
       <c r="F30">
         <v>61.49915804666827</v>
       </c>
       <c r="G30">
-        <v>15.48039451527544</v>
+        <v>23.02044743805629</v>
       </c>
     </row>
     <row r="31">
@@ -1123,22 +1123,22 @@
         </is>
       </c>
       <c r="B31">
+        <v>23.64508738223176</v>
+      </c>
+      <c r="C31">
         <v>26.58454141023929</v>
-      </c>
-      <c r="C31">
-        <v>23.64508738223176</v>
       </c>
       <c r="D31">
         <v>3.761584541062802</v>
       </c>
       <c r="E31">
+        <v>15.73929694980167</v>
+      </c>
+      <c r="F31">
+        <v>66.5647654219669</v>
+      </c>
+      <c r="G31">
         <v>17.69593762823143</v>
-      </c>
-      <c r="F31">
-        <v>66.56476542196691</v>
-      </c>
-      <c r="G31">
-        <v>15.73929694980167</v>
       </c>
     </row>
     <row r="32">
@@ -1148,22 +1148,22 @@
         </is>
       </c>
       <c r="B32">
+        <v>25.80925483380404</v>
+      </c>
+      <c r="C32">
         <v>34.97899920341806</v>
-      </c>
-      <c r="C32">
-        <v>25.80925483380404</v>
       </c>
       <c r="D32">
         <v>2.858858237151286</v>
       </c>
       <c r="E32">
-        <v>21.75469807348023</v>
+        <v>16.05170414241158</v>
       </c>
       <c r="F32">
         <v>62.19359778410819</v>
       </c>
       <c r="G32">
-        <v>16.05170414241158</v>
+        <v>21.75469807348023</v>
       </c>
     </row>
     <row r="33">
@@ -1173,22 +1173,22 @@
         </is>
       </c>
       <c r="B33">
+        <v>24.05930162552679</v>
+      </c>
+      <c r="C33">
         <v>40.68332329921734</v>
-      </c>
-      <c r="C33">
-        <v>24.05930162552679</v>
       </c>
       <c r="D33">
         <v>2.458009618941916</v>
       </c>
       <c r="E33">
-        <v>24.69508016993285</v>
+        <v>14.60417523183043</v>
       </c>
       <c r="F33">
         <v>60.70074459823672</v>
       </c>
       <c r="G33">
-        <v>14.60417523183043</v>
+        <v>24.69508016993285</v>
       </c>
     </row>
     <row r="34">
@@ -1198,22 +1198,22 @@
         </is>
       </c>
       <c r="B34">
+        <v>27.94965593388577</v>
+      </c>
+      <c r="C34">
         <v>29.07749015759008</v>
-      </c>
-      <c r="C34">
-        <v>27.94965593388577</v>
       </c>
       <c r="D34">
         <v>3.439086367428347</v>
       </c>
       <c r="E34">
-        <v>18.51749260006996</v>
+        <v>17.79925104007415</v>
       </c>
       <c r="F34">
         <v>63.68325635985589</v>
       </c>
       <c r="G34">
-        <v>17.79925104007415</v>
+        <v>18.51749260006996</v>
       </c>
     </row>
     <row r="35">
@@ -1223,22 +1223,22 @@
         </is>
       </c>
       <c r="B35">
+        <v>23.6739806496199</v>
+      </c>
+      <c r="C35">
         <v>30.06651693158258</v>
-      </c>
-      <c r="C35">
-        <v>23.6739806496199</v>
       </c>
       <c r="D35">
         <v>3.325958913949145</v>
       </c>
       <c r="E35">
-        <v>19.55666685396415</v>
+        <v>15.39866269595999</v>
       </c>
       <c r="F35">
         <v>65.04467045007586</v>
       </c>
       <c r="G35">
-        <v>15.39866269595999</v>
+        <v>19.55666685396415</v>
       </c>
     </row>
     <row r="36">
@@ -1248,22 +1248,22 @@
         </is>
       </c>
       <c r="B36">
+        <v>25.6521016780196</v>
+      </c>
+      <c r="C36">
         <v>36.69214155175278</v>
-      </c>
-      <c r="C36">
-        <v>25.6521016780196</v>
       </c>
       <c r="D36">
         <v>2.725379216662893</v>
       </c>
       <c r="E36">
+        <v>15.80105408586194</v>
+      </c>
+      <c r="F36">
+        <v>61.59750294222995</v>
+      </c>
+      <c r="G36">
         <v>22.6014429719081</v>
-      </c>
-      <c r="F36">
-        <v>61.59750294222994</v>
-      </c>
-      <c r="G36">
-        <v>15.80105408586194</v>
       </c>
     </row>
     <row r="37">
@@ -1273,22 +1273,22 @@
         </is>
       </c>
       <c r="B37">
+        <v>34.9469918333708</v>
+      </c>
+      <c r="C37">
         <v>18.90687045778078</v>
-      </c>
-      <c r="C37">
-        <v>34.9469918333708</v>
       </c>
       <c r="D37">
         <v>5.289082623340598</v>
       </c>
       <c r="E37">
-        <v>12.28885006604618</v>
+        <v>22.71440658879102</v>
       </c>
       <c r="F37">
         <v>64.99674334516281</v>
       </c>
       <c r="G37">
-        <v>22.71440658879102</v>
+        <v>12.28885006604618</v>
       </c>
     </row>
     <row r="38">
@@ -1298,22 +1298,22 @@
         </is>
       </c>
       <c r="B38">
+        <v>35.79242671109532</v>
+      </c>
+      <c r="C38">
         <v>17.30144923985348</v>
-      </c>
-      <c r="C38">
-        <v>35.79242671109532</v>
       </c>
       <c r="D38">
         <v>5.779862635417405</v>
       </c>
       <c r="E38">
-        <v>11.30120269826917</v>
+        <v>23.3793980907265</v>
       </c>
       <c r="F38">
         <v>65.31939921100432</v>
       </c>
       <c r="G38">
-        <v>23.3793980907265</v>
+        <v>11.30120269826917</v>
       </c>
     </row>
     <row r="39">
@@ -1323,22 +1323,22 @@
         </is>
       </c>
       <c r="B39">
+        <v>33.90350877192982</v>
+      </c>
+      <c r="C39">
         <v>17.79239766081871</v>
-      </c>
-      <c r="C39">
-        <v>33.90350877192982</v>
       </c>
       <c r="D39">
         <v>5.62037797863599</v>
       </c>
       <c r="E39">
-        <v>11.7289899768697</v>
+        <v>22.34965304548959</v>
       </c>
       <c r="F39">
         <v>65.92135697764071</v>
       </c>
       <c r="G39">
-        <v>22.34965304548959</v>
+        <v>11.7289899768697</v>
       </c>
     </row>
     <row r="40">
@@ -1348,22 +1348,22 @@
         </is>
       </c>
       <c r="B40">
+        <v>30.66593404336172</v>
+      </c>
+      <c r="C40">
         <v>27.21250526359033</v>
-      </c>
-      <c r="C40">
-        <v>30.66593404336172</v>
       </c>
       <c r="D40">
         <v>3.674781099033817</v>
       </c>
       <c r="E40">
-        <v>17.23636576536138</v>
+        <v>19.42376310405507</v>
       </c>
       <c r="F40">
         <v>63.33987113058356</v>
       </c>
       <c r="G40">
-        <v>19.42376310405507</v>
+        <v>17.23636576536138</v>
       </c>
     </row>
     <row r="41">
@@ -1373,22 +1373,22 @@
         </is>
       </c>
       <c r="B41">
+        <v>31.9653520572216</v>
+      </c>
+      <c r="C41">
         <v>24.19318852943107</v>
-      </c>
-      <c r="C41">
-        <v>31.9653520572216</v>
       </c>
       <c r="D41">
         <v>4.13339481393078</v>
       </c>
       <c r="E41">
-        <v>15.4927091650208</v>
+        <v>20.46980711854436</v>
       </c>
       <c r="F41">
         <v>64.03748371643485</v>
       </c>
       <c r="G41">
-        <v>20.46980711854436</v>
+        <v>15.4927091650208</v>
       </c>
     </row>
     <row r="42">
@@ -1398,22 +1398,22 @@
         </is>
       </c>
       <c r="B42">
+        <v>20.47803074855079</v>
+      </c>
+      <c r="C42">
         <v>28.31639082584222</v>
-      </c>
-      <c r="C42">
-        <v>20.47803074855079</v>
       </c>
       <c r="D42">
         <v>3.531523512831924</v>
       </c>
       <c r="E42">
-        <v>19.03054598836881</v>
+        <v>13.76263339167749</v>
       </c>
       <c r="F42">
         <v>67.20682061995369</v>
       </c>
       <c r="G42">
-        <v>13.76263339167749</v>
+        <v>19.03054598836881</v>
       </c>
     </row>
     <row r="43">
@@ -1423,22 +1423,22 @@
         </is>
       </c>
       <c r="B43">
+        <v>30.51222762188431</v>
+      </c>
+      <c r="C43">
         <v>29.06803574227935</v>
-      </c>
-      <c r="C43">
-        <v>30.51222762188431</v>
       </c>
       <c r="D43">
         <v>3.44020493460968</v>
       </c>
       <c r="E43">
-        <v>18.21530753834252</v>
+        <v>19.12030158281862</v>
       </c>
       <c r="F43">
         <v>62.66439087883885</v>
       </c>
       <c r="G43">
-        <v>19.12030158281862</v>
+        <v>18.21530753834252</v>
       </c>
     </row>
     <row r="44">
@@ -1448,22 +1448,22 @@
         </is>
       </c>
       <c r="B44">
+        <v>30.19117198703689</v>
+      </c>
+      <c r="C44">
         <v>32.23839474248805</v>
-      </c>
-      <c r="C44">
-        <v>30.19117198703689</v>
       </c>
       <c r="D44">
         <v>3.101891418563923</v>
       </c>
       <c r="E44">
-        <v>19.84761481028322</v>
+        <v>18.58723913073704</v>
       </c>
       <c r="F44">
         <v>61.56514605897975</v>
       </c>
       <c r="G44">
-        <v>18.58723913073704</v>
+        <v>19.84761481028322</v>
       </c>
     </row>
     <row r="45">
@@ -1473,22 +1473,22 @@
         </is>
       </c>
       <c r="B45">
+        <v>33.80997177798683</v>
+      </c>
+      <c r="C45">
         <v>30.63029162746943</v>
-      </c>
-      <c r="C45">
-        <v>33.80997177798683</v>
       </c>
       <c r="D45">
         <v>3.264742014742015</v>
       </c>
       <c r="E45">
-        <v>18.62700228832951</v>
+        <v>20.56064073226544</v>
       </c>
       <c r="F45">
         <v>60.81235697940502</v>
       </c>
       <c r="G45">
-        <v>20.56064073226544</v>
+        <v>18.62700228832951</v>
       </c>
     </row>
     <row r="46">
@@ -1498,22 +1498,22 @@
         </is>
       </c>
       <c r="B46">
+        <v>29.87188426006624</v>
+      </c>
+      <c r="C46">
         <v>34.70454941607112</v>
-      </c>
-      <c r="C46">
-        <v>29.87188426006624</v>
       </c>
       <c r="D46">
         <v>2.881466599698644</v>
       </c>
       <c r="E46">
-        <v>21.08719252257262</v>
+        <v>18.1507665422194</v>
       </c>
       <c r="F46">
         <v>60.76204093520798</v>
       </c>
       <c r="G46">
-        <v>18.1507665422194</v>
+        <v>21.08719252257262</v>
       </c>
     </row>
     <row r="47">
@@ -1523,22 +1523,22 @@
         </is>
       </c>
       <c r="B47">
+        <v>30.47210300429185</v>
+      </c>
+      <c r="C47">
         <v>35.28296237149416</v>
-      </c>
-      <c r="C47">
-        <v>30.47210300429185</v>
       </c>
       <c r="D47">
         <v>2.834229137199434</v>
       </c>
       <c r="E47">
-        <v>21.28620461251279</v>
+        <v>18.38381405431444</v>
       </c>
       <c r="F47">
         <v>60.32998133317275</v>
       </c>
       <c r="G47">
-        <v>18.38381405431444</v>
+        <v>21.28620461251279</v>
       </c>
     </row>
     <row r="48">
@@ -1548,22 +1548,22 @@
         </is>
       </c>
       <c r="B48">
+        <v>33.3182503770739</v>
+      </c>
+      <c r="C48">
         <v>39.30618401206637</v>
-      </c>
-      <c r="C48">
-        <v>33.3182503770739</v>
       </c>
       <c r="D48">
         <v>2.544128933231006</v>
       </c>
       <c r="E48">
-        <v>22.76976845784186</v>
+        <v>19.30100480559196</v>
       </c>
       <c r="F48">
         <v>57.92922673656619</v>
       </c>
       <c r="G48">
-        <v>19.30100480559196</v>
+        <v>22.76976845784185</v>
       </c>
     </row>
     <row r="49">
@@ -1573,22 +1573,22 @@
         </is>
       </c>
       <c r="B49">
+        <v>28.76666337513577</v>
+      </c>
+      <c r="C49">
         <v>30.31104966920115</v>
-      </c>
-      <c r="C49">
-        <v>28.76666337513577</v>
       </c>
       <c r="D49">
         <v>3.299126922074537</v>
       </c>
       <c r="E49">
-        <v>19.05424027610523</v>
+        <v>18.08340264931905</v>
       </c>
       <c r="F49">
         <v>62.86235707457573</v>
       </c>
       <c r="G49">
-        <v>18.08340264931905</v>
+        <v>19.05424027610523</v>
       </c>
     </row>
     <row r="50">
@@ -1598,22 +1598,22 @@
         </is>
       </c>
       <c r="B50">
+        <v>30.6238260800064</v>
+      </c>
+      <c r="C50">
         <v>30.33609079646725</v>
-      </c>
-      <c r="C50">
-        <v>30.6238260800064</v>
       </c>
       <c r="D50">
         <v>3.2964036358846</v>
       </c>
       <c r="E50">
-        <v>18.84698463142737</v>
+        <v>19.02574670407429</v>
       </c>
       <c r="F50">
         <v>62.12726866449835</v>
       </c>
       <c r="G50">
-        <v>19.02574670407429</v>
+        <v>18.84698463142737</v>
       </c>
     </row>
     <row r="51">
@@ -1623,22 +1623,22 @@
         </is>
       </c>
       <c r="B51">
+        <v>28.1533688282836</v>
+      </c>
+      <c r="C51">
         <v>29.46336231662006</v>
-      </c>
-      <c r="C51">
-        <v>28.1533688282836</v>
       </c>
       <c r="D51">
         <v>3.394045761830473</v>
       </c>
       <c r="E51">
-        <v>18.69304235825901</v>
+        <v>17.86191644997448</v>
       </c>
       <c r="F51">
         <v>63.44504119176651</v>
       </c>
       <c r="G51">
-        <v>17.86191644997448</v>
+        <v>18.69304235825901</v>
       </c>
     </row>
     <row r="52">
@@ -1648,22 +1648,22 @@
         </is>
       </c>
       <c r="B52">
+        <v>30.96540550843419</v>
+      </c>
+      <c r="C52">
         <v>23.440388830649</v>
-      </c>
-      <c r="C52">
-        <v>30.96540550843419</v>
       </c>
       <c r="D52">
         <v>4.266140835908278</v>
       </c>
       <c r="E52">
-        <v>15.1810292683529</v>
+        <v>20.05456183880803</v>
       </c>
       <c r="F52">
         <v>64.76440889283907</v>
       </c>
       <c r="G52">
-        <v>20.05456183880803</v>
+        <v>15.1810292683529</v>
       </c>
     </row>
     <row r="53">
@@ -1673,22 +1673,22 @@
         </is>
       </c>
       <c r="B53">
+        <v>28.22055873575028</v>
+      </c>
+      <c r="C53">
         <v>29.18114062984165</v>
-      </c>
-      <c r="C53">
-        <v>28.22055873575028</v>
       </c>
       <c r="D53">
         <v>3.42687084334656</v>
       </c>
       <c r="E53">
-        <v>18.53927927554552</v>
+        <v>17.92900511842841</v>
       </c>
       <c r="F53">
         <v>63.53171560602607</v>
       </c>
       <c r="G53">
-        <v>17.92900511842841</v>
+        <v>18.53927927554552</v>
       </c>
     </row>
   </sheetData>
